--- a/scenarios/05_tom_optical_designer/5.3_mono_vs_poly_psf/outputs/chromatic_psf_results.xlsx
+++ b/scenarios/05_tom_optical_designer/5.3_mono_vs_poly_psf/outputs/chromatic_psf_results.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,15 +460,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>FWHM [µm]</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>SNR</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Signal [e⁻]</t>
         </is>
@@ -485,21 +490,24 @@
         <v>0.78</v>
       </c>
       <c r="D2" t="n">
-        <v>0.518</v>
+        <v>0.3077</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7385</v>
+        <v>0.5205</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.9022</v>
       </c>
       <c r="G2" t="n">
-        <v>14.4</v>
+        <v>0.6468</v>
       </c>
       <c r="H2" t="n">
-        <v>116.7</v>
+        <v>20.3</v>
       </c>
       <c r="I2" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="J2" t="n">
         <v>27244</v>
       </c>
     </row>
@@ -514,21 +522,24 @@
         <v>0.89</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4538</v>
+        <v>0.2904</v>
       </c>
       <c r="E3" t="n">
-        <v>0.668</v>
+        <v>0.5032</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8981</v>
+        <v>0.8892</v>
       </c>
       <c r="G3" t="n">
-        <v>16.5</v>
+        <v>0.6276</v>
       </c>
       <c r="H3" t="n">
-        <v>126.7</v>
+        <v>20.5</v>
       </c>
       <c r="I3" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="J3" t="n">
         <v>31319</v>
       </c>
     </row>
@@ -543,21 +554,24 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4224</v>
+        <v>0.2534</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6367</v>
+        <v>0.4701</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8893</v>
+        <v>0.8823</v>
       </c>
       <c r="G4" t="n">
-        <v>17.5</v>
+        <v>0.6016</v>
       </c>
       <c r="H4" t="n">
-        <v>142.7</v>
+        <v>21.8</v>
       </c>
       <c r="I4" t="n">
+        <v>154.2</v>
+      </c>
+      <c r="J4" t="n">
         <v>40142</v>
       </c>
     </row>
@@ -572,21 +586,24 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3915</v>
+        <v>0.265</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.4483</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8761</v>
+        <v>0.8743</v>
       </c>
       <c r="G5" t="n">
-        <v>18.5</v>
+        <v>0.6097</v>
       </c>
       <c r="H5" t="n">
-        <v>157.2</v>
+        <v>21.5</v>
       </c>
       <c r="I5" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="J5" t="n">
         <v>49923</v>
       </c>
     </row>
@@ -601,21 +618,24 @@
         <v>1.11</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3315</v>
+        <v>0.2026</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5039</v>
+        <v>0.389</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8612</v>
       </c>
       <c r="G6" t="n">
-        <v>20.6</v>
+        <v>0.5632</v>
       </c>
       <c r="H6" t="n">
-        <v>162.2</v>
+        <v>23.9</v>
       </c>
       <c r="I6" t="n">
+        <v>187.3</v>
+      </c>
+      <c r="J6" t="n">
         <v>59348</v>
       </c>
     </row>
@@ -630,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,15 +681,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>FWHM [µm]</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>SNR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>NEDT [K]</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>NIIRS</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Signal [e⁻]</t>
         </is>
@@ -685,21 +720,30 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4223</v>
+        <v>0.2532</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6365</v>
+        <v>0.4699</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8893</v>
+        <v>0.8822</v>
       </c>
       <c r="F2" t="n">
-        <v>17.5</v>
+        <v>0.6014</v>
       </c>
       <c r="G2" t="n">
-        <v>468.4</v>
+        <v>21.8</v>
       </c>
       <c r="H2" t="n">
+        <v>516.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K2" t="n">
         <v>500000</v>
       </c>
     </row>
@@ -713,21 +757,30 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4027</v>
+        <v>0.2461</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5871</v>
+        <v>0.4353</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8796</v>
+        <v>0.8766</v>
       </c>
       <c r="F3" t="n">
-        <v>16.7</v>
+        <v>0.5966</v>
       </c>
       <c r="G3" t="n">
-        <v>468.4</v>
+        <v>21.3</v>
       </c>
       <c r="H3" t="n">
+        <v>516.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K3" t="n">
         <v>500000</v>
       </c>
     </row>
@@ -741,21 +794,30 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4047</v>
+        <v>0.2473</v>
       </c>
       <c r="D4" t="n">
-        <v>0.589</v>
+        <v>0.4364</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8804</v>
+        <v>0.8769</v>
       </c>
       <c r="F4" t="n">
-        <v>16.7</v>
+        <v>0.5972</v>
       </c>
       <c r="G4" t="n">
-        <v>468.4</v>
+        <v>21.2</v>
       </c>
       <c r="H4" t="n">
+        <v>516.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K4" t="n">
         <v>500000</v>
       </c>
     </row>
@@ -769,21 +831,30 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4055</v>
+        <v>0.2478</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5899</v>
+        <v>0.4369</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8807</v>
+        <v>0.8771</v>
       </c>
       <c r="F5" t="n">
-        <v>16.8</v>
+        <v>0.5977</v>
       </c>
       <c r="G5" t="n">
-        <v>468.4</v>
+        <v>21.2</v>
       </c>
       <c r="H5" t="n">
+        <v>516.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K5" t="n">
         <v>500000</v>
       </c>
     </row>
@@ -802,7 +873,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>+4.3%</t>
+          <t>+2.4%</t>
         </is>
       </c>
     </row>
@@ -814,7 +885,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>+8.1%</t>
+          <t>+7.7%</t>
         </is>
       </c>
     </row>
@@ -826,7 +897,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+0.6%</t>
         </is>
       </c>
     </row>
@@ -838,7 +909,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+4.6%</t>
+          <t>+3.0%</t>
         </is>
       </c>
     </row>
@@ -936,7 +1007,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>+4.3%</t>
+          <t>+2.4%</t>
         </is>
       </c>
     </row>
@@ -948,7 +1019,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+8.1%</t>
+          <t>+7.7%</t>
         </is>
       </c>
     </row>
@@ -960,7 +1031,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+4.6%</t>
+          <t>+3.0%</t>
         </is>
       </c>
     </row>
